--- a/mappingCorps/ig/FRMedicationLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRMedicationLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMProduitSante vers le profil CDA FRCDAProduitDeSante, puis vers le profil FHIR FRMedicationDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMMedication vers le profil CDA FRCDAProduitDeSante (Groupe 1), et vers le profil FHIR FRMedicationDocument (Groupe 2).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-produit-sante</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-medication</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-produit-de-sante</t>
   </si>
   <si>
-    <t>FRLMProduitSante</t>
+    <t>FRLMMedication</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,66 +118,75 @@
     <t>FRCDAProduitDeSante</t>
   </si>
   <si>
-    <t>FRLMProduitSante.medicament</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.manufacturedProduct.manufacturedMaterial</t>
-  </si>
-  <si>
-    <t>FRLMProduitSante.medicament.code</t>
+    <t>FRLMMedication.identifyingCode[x]</t>
   </si>
   <si>
     <t>FRCDAProduitDeSante.manufacturedProduct.manufacturedMaterial.code</t>
   </si>
   <si>
-    <t>FRLMProduitSante.medicament.code.autreCodification</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.manufacturedProduct.manufacturedMaterial.code.translation</t>
-  </si>
-  <si>
-    <t>FRLMProduitSante.nomProduit</t>
+    <t>FRLMMedication.classification</t>
+  </si>
+  <si>
+    <t>FRCDAProduitDeSante.pharm:asSpecializedKind</t>
+  </si>
+  <si>
+    <t>FRLMMedication.productName</t>
   </si>
   <si>
     <t>FRCDAProduitDeSante.manufacturedProduct.manufacturedMaterial.name</t>
   </si>
   <si>
-    <t>FRLMProduitSante.formeGalenique</t>
+    <t>FRLMMedication.item.doseForm</t>
   </si>
   <si>
     <t>FRCDAProduitDeSante.manufacturedProduct.manufacturedMaterial.pharm:formCode</t>
   </si>
   <si>
-    <t>FRLMProduitSante.numeroLot</t>
+    <t>FRLMMedication.item.ingredient.substance</t>
+  </si>
+  <si>
+    <t>FRCDAProduitDeSante.pharm:ingredient.pharm:ingredient.pharm:code</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.ingredient.strengthInfo.strength</t>
+  </si>
+  <si>
+    <t>FRCDAProduitDeSante.pharm:ingredient.pharm:quantity</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.unitOfPresentation</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>FRCDAProduitDeSante.pharm:asContent</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.containedQuantity</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.amount</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.packageType</t>
+  </si>
+  <si>
+    <t>FRCDAProduitDeSante.pharm:asContent.pharm:containerPackagedMedicine</t>
+  </si>
+  <si>
+    <t>FRLMMedication.batch.lotNumber</t>
   </si>
   <si>
     <t>FRCDAProduitDeSante.manufacturedProduct.manufacturedMaterial.lotNumberText</t>
   </si>
   <si>
-    <t>FRLMProduitSante.dateExpiration</t>
+    <t>FRLMMedication.batch.expirationDate</t>
   </si>
   <si>
     <t>FRCDAProduitDeSante.pharm:expirationTime</t>
   </si>
   <si>
-    <t>FRLMProduitSante.conditionnement</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.pharm:asContent</t>
-  </si>
-  <si>
-    <t>FRLMProduitSante.equivalentGenerique</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.pharm:asSpecializedKind</t>
-  </si>
-  <si>
-    <t>FRLMProduitSante.substanceActive</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.pharm:ingredient</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-medication-document</t>
   </si>
   <si>
@@ -187,46 +196,52 @@
     <t>FRMedicationDocument.code</t>
   </si>
   <si>
-    <t>FRMedicationDocument.code.coding</t>
+    <t>FRMedicationDocument.extension:ihe-ext-medication-classification</t>
   </si>
   <si>
     <t>FRMedicationDocument.extension:ihe-ext-medication-productname</t>
   </si>
   <si>
+    <t>FRLMMedication.marketingAuthorisationHolder</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument.manufacturer</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument.ingredient.itemReference</t>
+  </si>
+  <si>
     <t>FRMedicationDocument.form</t>
   </si>
   <si>
+    <t>FRLMMedication.item.ingredient</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument.ingredient</t>
+  </si>
+  <si>
+    <t>FRLMMedication.item.ingredient.isActive</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument.ingredient.isActive</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument.ingredient.itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument.ingredient:substanceActive.strength</t>
+  </si>
+  <si>
+    <t>FRMedicationDocument.amount</t>
+  </si>
+  <si>
     <t>FRMedicationDocument.batch.lotNumber</t>
   </si>
   <si>
     <t>FRMedicationDocument.batch.expirationDate</t>
-  </si>
-  <si>
-    <t>FRMedicationDocument.extension:ihe-ext-medication-characteristic</t>
-  </si>
-  <si>
-    <t>FRMedicationDocument.extension:ihe-ext-medication-classification</t>
-  </si>
-  <si>
-    <t>FRMedicationDocument.ingredient:substanceActive</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.pharm:ingredient.pharm:quantity</t>
-  </si>
-  <si>
-    <t>FRMedicationDocument.ingredient:substanceActive.strength</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.pharm:ingredient.pharm:ingredient.pharm:code</t>
-  </si>
-  <si>
-    <t>FRMedicationDocument.ingredient:substanceActive.itemCodeableConcept</t>
-  </si>
-  <si>
-    <t>FRCDAProduitDeSante.pharm:ingredient.pharm:ingredient.pharm:name</t>
-  </si>
-  <si>
-    <t>FRMedicationDocument.ingredient:substanceActive.itemCodeableConcept.text</t>
   </si>
 </sst>
 </file>
@@ -478,7 +493,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -612,23 +627,23 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -641,22 +656,48 @@
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E15" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -665,7 +706,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -687,7 +728,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -696,7 +737,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -704,172 +745,196 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="D15" t="s" s="2">
-        <v>70</v>
-      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E17" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
